--- a/Employee Data/PASSPORT_Renewal Request.xlsx
+++ b/Employee Data/PASSPORT_Renewal Request.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\servadmin\Desktop\Saudi Ic\Employee Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECB2BB87-48E2-4165-8907-C22101FBA8AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4355C5DB-5ADB-4F6C-9BC9-28A5465107E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B52C8B97-A5EC-5C45-A769-A0F3D3DD4086}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="29">
   <si>
     <t>NAME</t>
   </si>
@@ -51,9 +51,6 @@
     <t>ID NO.</t>
   </si>
   <si>
-    <t>Nataionalty</t>
-  </si>
-  <si>
     <t>Passport Renewal Request</t>
   </si>
   <si>
@@ -69,18 +66,6 @@
     <t>India</t>
   </si>
   <si>
-    <t>prem sagar</t>
-  </si>
-  <si>
-    <t>Mainuddin Ansari</t>
-  </si>
-  <si>
-    <t>Saddam Ali</t>
-  </si>
-  <si>
-    <t>31/07/2025</t>
-  </si>
-  <si>
     <t>To Pick Passport</t>
   </si>
   <si>
@@ -99,9 +84,6 @@
     <t>18/01/2026</t>
   </si>
   <si>
-    <t>13/01/ 2026</t>
-  </si>
-  <si>
     <t>Abdel kareem Aitba</t>
   </si>
   <si>
@@ -120,49 +102,25 @@
     <t>Arun Pal</t>
   </si>
   <si>
-    <t>Adil</t>
-  </si>
-  <si>
-    <t>Anil kumar yadav</t>
-  </si>
-  <si>
-    <t>Abdullha al amin</t>
-  </si>
-  <si>
-    <t>Abdek malek Manjor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shamshad shek </t>
-  </si>
-  <si>
-    <t>Shiv Dayal sing</t>
-  </si>
-  <si>
-    <t>Muhammad Umar</t>
-  </si>
-  <si>
-    <t>Asgar miyan</t>
-  </si>
-  <si>
-    <t>21/1/2026</t>
-  </si>
-  <si>
     <t>naresh mahra</t>
   </si>
   <si>
-    <t>26/1/2026</t>
-  </si>
-  <si>
-    <t>Nasir</t>
-  </si>
-  <si>
-    <t>0574760050</t>
-  </si>
-  <si>
     <t>Indra kamal Jeet</t>
   </si>
   <si>
     <t>0536567158</t>
+  </si>
+  <si>
+    <t>NATIONALITY</t>
+  </si>
+  <si>
+    <t>Imran</t>
+  </si>
+  <si>
+    <t>0583955873</t>
+  </si>
+  <si>
+    <t>Renewal</t>
   </si>
 </sst>
 </file>
@@ -234,7 +192,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -257,17 +215,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -279,7 +226,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -307,9 +253,14 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -625,460 +576,243 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{646D3CE3-3021-5A4E-B3F8-2D54A587E4BC}">
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.296875" style="3" customWidth="1"/>
     <col min="3" max="3" width="18.296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.69921875" style="17" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.69921875" style="16" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19.69921875" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.796875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.8984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.8984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="4"/>
-      <c r="B1" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="5"/>
+      <c r="A1" s="17"/>
+      <c r="B1" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="4"/>
     </row>
     <row r="2" spans="1:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="4"/>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="5"/>
+      <c r="A2" s="17"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="4"/>
     </row>
     <row r="3" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="16" t="s">
+      <c r="D3" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="6" t="s">
-        <v>5</v>
+      <c r="F3" s="5" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="8">
         <v>1</v>
       </c>
-      <c r="B4" s="9">
+      <c r="B4" s="8">
         <v>3139</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="8">
+        <v>577468451</v>
+      </c>
+      <c r="E4" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="9">
-        <v>577468451</v>
-      </c>
-      <c r="E4" s="9" t="s">
+      <c r="F4" s="7" t="s">
         <v>8</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="8">
-        <v>2</v>
-      </c>
-      <c r="B5" s="9">
-        <v>4444</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="D5" s="9">
-        <v>543897852</v>
-      </c>
-      <c r="E5" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+      <c r="B5" s="8">
+        <v>4164</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="8">
+        <v>572530270</v>
+      </c>
+      <c r="E5" s="12">
+        <v>45942</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B6" s="9">
-        <v>2940</v>
+        <v>4271</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D6" s="9">
-        <v>574948683</v>
+        <v>551289037</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>10</v>
+        <v>15</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="8">
-        <v>4</v>
-      </c>
-      <c r="B7" s="9">
-        <v>3265</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" s="9">
-        <v>506331059</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>10</v>
+        <v>5</v>
+      </c>
+      <c r="B7" s="8">
+        <v>4496</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="8">
+        <v>530361335</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="8">
-        <v>5</v>
-      </c>
-      <c r="B8" s="9">
-        <v>2215</v>
-      </c>
-      <c r="C8" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="8">
+        <v>2178</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="13">
+        <v>507726497</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="F8" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="9">
-        <v>596766323</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>16</v>
-      </c>
+      <c r="G8" s="2"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="8">
-        <v>6</v>
-      </c>
-      <c r="B9" s="9">
-        <v>4164</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" s="9">
-        <v>572530270</v>
-      </c>
-      <c r="E9" s="13">
-        <v>45942</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" s="12" customFormat="1" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+      <c r="B9" s="8">
+        <v>2660</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="13">
+        <v>540481087</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9" s="2"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="8">
-        <v>7</v>
-      </c>
-      <c r="B10" s="10">
-        <v>4271</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10" s="10">
-        <v>551289037</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="F10" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="8">
+        <v>4155</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" s="8">
+        <v>530509672</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" s="14" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="8">
-        <v>8</v>
-      </c>
-      <c r="B11" s="9">
-        <v>4496</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="D11" s="9">
-        <v>530361335</v>
-      </c>
-      <c r="E11" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="8">
+        <v>2953</v>
+      </c>
+      <c r="C11" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="F11" s="11" t="s">
+      <c r="D11" s="19" t="s">
         <v>24</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="8">
+        <v>10</v>
+      </c>
+      <c r="B12" s="8">
+        <v>2143</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="F12" s="14" t="s">
         <v>9</v>
-      </c>
-      <c r="B12" s="9">
-        <v>2178</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="D12" s="14">
-        <v>507726497</v>
-      </c>
-      <c r="E12" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="F12" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="G12" s="2"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="8">
-        <v>10</v>
-      </c>
-      <c r="B13" s="9">
-        <v>2660</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="D13" s="14">
-        <v>540481087</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="F13" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" s="8">
-        <v>11</v>
-      </c>
-      <c r="B14" s="9">
-        <v>3091</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="D14" s="14">
-        <v>597389395</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="F14" s="15" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="8">
-        <v>12</v>
-      </c>
-      <c r="B15" s="9">
-        <v>4240</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="D15" s="14">
-        <v>571572167</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="F15" s="15" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A16" s="8">
-        <v>13</v>
-      </c>
-      <c r="B16" s="9">
-        <v>2809</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D16" s="9">
-        <v>573136620</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="F16" s="15" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="8">
-        <v>14</v>
-      </c>
-      <c r="B17" s="9">
-        <v>2906</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D17" s="14">
-        <v>556526257</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="F17" s="15" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="8">
-        <v>15</v>
-      </c>
-      <c r="B18" s="9">
-        <v>3362</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="D18" s="9">
-        <v>566124787</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="F18" s="15" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="8">
-        <v>16</v>
-      </c>
-      <c r="B19" s="9">
-        <v>3275</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="D19" s="9">
-        <v>590384802</v>
-      </c>
-      <c r="E19" s="13">
-        <v>45696</v>
-      </c>
-      <c r="F19" s="15" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="8">
-        <v>17</v>
-      </c>
-      <c r="B20" s="9">
-        <v>3281</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D20" s="9">
-        <v>575611498</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F20" s="15" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="8">
-        <v>18</v>
-      </c>
-      <c r="B21" s="9">
-        <v>4155</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D21" s="9">
-        <v>530509672</v>
-      </c>
-      <c r="E21" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="F21" s="15" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="8">
-        <v>19</v>
-      </c>
-      <c r="B22" s="3">
-        <v>2162</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D22" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="E22" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="F22" s="18" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="8">
-        <v>20</v>
-      </c>
-      <c r="B23" s="3">
-        <v>2953</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D23" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="E23" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="F23" s="18" t="s">
-        <v>18</v>
       </c>
     </row>
   </sheetData>
